--- a/raw/1952election.xlsx
+++ b/raw/1952election.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Dropbox/MyData/USvoting/historical voting/1920to1974/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8194D3-6131-A64B-9913-4F9B29832845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98166EFE-EE5E-F849-97CA-EEF88D84ABCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="16520" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6447" uniqueCount="1941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6446" uniqueCount="1941">
   <si>
     <t>State</t>
   </si>
@@ -7843,7 +7843,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E52" t="s">
         <v>93</v>
@@ -8321,8 +8321,8 @@
       <c r="C73" t="s">
         <v>7</v>
       </c>
-      <c r="D73" t="s">
-        <v>113</v>
+      <c r="D73">
+        <v>16</v>
       </c>
       <c r="E73" t="s">
         <v>116</v>
